--- a/out/07_Ops/SNX-OPS-RPT-01 Operations KPI Performance Report (Rev00 DRAFT).xlsx
+++ b/out/07_Ops/SNX-OPS-RPT-01 Operations KPI Performance Report (Rev00 DRAFT).xlsx
@@ -12,7 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Narasi Bulanan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'KPI'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -171,7 +173,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -334,6 +336,45 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -673,8 +714,15 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="28">
-      <c r="A4" s="31" t="inlineStr">
+    <row r="3" s="28">
+      <c r="A3" s="55" t="n"/>
+      <c r="B3" s="55" t="n"/>
+      <c r="C3" s="55" t="n"/>
+      <c r="D3" s="55" t="n"/>
+      <c r="E3" s="55" t="n"/>
+    </row>
+    <row r="4" ht="16.5" customHeight="1" s="28">
+      <c r="A4" s="53" t="inlineStr">
         <is>
           <t>Nomor dokumen</t>
         </is>
@@ -684,9 +732,12 @@
           <t>SNX-OPS-RPT-01</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="28">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="C4" s="55" t="n"/>
+      <c r="D4" s="55" t="n"/>
+      <c r="E4" s="55" t="n"/>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" s="28">
+      <c r="A5" s="53" t="inlineStr">
         <is>
           <t>Judul</t>
         </is>
@@ -696,9 +747,12 @@
           <t>Operations KPI &amp; Performance Monitoring Report</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="28">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="C5" s="55" t="n"/>
+      <c r="D5" s="55" t="n"/>
+      <c r="E5" s="55" t="n"/>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" s="28">
+      <c r="A6" s="53" t="inlineStr">
         <is>
           <t>Revisi</t>
         </is>
@@ -708,9 +762,12 @@
           <t>00 (Draft)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="28">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="C6" s="55" t="n"/>
+      <c r="D6" s="55" t="n"/>
+      <c r="E6" s="55" t="n"/>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" s="28">
+      <c r="A7" s="53" t="inlineStr">
         <is>
           <t>Tanggal draft</t>
         </is>
@@ -720,9 +777,12 @@
           <t>13 Oktober 2026</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="28">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="C7" s="55" t="n"/>
+      <c r="D7" s="55" t="n"/>
+      <c r="E7" s="55" t="n"/>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" s="28">
+      <c r="A8" s="53" t="inlineStr">
         <is>
           <t>Tanggal efektif</t>
         </is>
@@ -732,9 +792,12 @@
           <t>Ditetapkan saat pengesahan</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="28">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="C8" s="55" t="n"/>
+      <c r="D8" s="55" t="n"/>
+      <c r="E8" s="55" t="n"/>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" s="28">
+      <c r="A9" s="53" t="inlineStr">
         <is>
           <t>Klasifikasi</t>
         </is>
@@ -744,9 +807,12 @@
           <t>RESTRICTED (Internal)</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="28">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="C9" s="55" t="n"/>
+      <c r="D9" s="55" t="n"/>
+      <c r="E9" s="55" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="28">
+      <c r="A10" s="53" t="inlineStr">
         <is>
           <t>Pemilik dokumen</t>
         </is>
@@ -756,9 +822,12 @@
           <t>Head of Operation</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="28">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="C10" s="55" t="n"/>
+      <c r="D10" s="55" t="n"/>
+      <c r="E10" s="55" t="n"/>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="28">
+      <c r="A11" s="53" t="inlineStr">
         <is>
           <t>Disetujui oleh</t>
         </is>
@@ -768,9 +837,12 @@
           <t>Samuel Kristanto Utomo / President Director</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="28">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="C11" s="55" t="n"/>
+      <c r="D11" s="55" t="n"/>
+      <c r="E11" s="55" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="28">
+      <c r="A12" s="53" t="inlineStr">
         <is>
           <t>Acuan ISO 9001:2015</t>
         </is>
@@ -780,9 +852,12 @@
           <t>Klausul 9.1, 9.3.2</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="28">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="C12" s="55" t="n"/>
+      <c r="D12" s="55" t="n"/>
+      <c r="E12" s="55" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="28">
+      <c r="A13" s="53" t="inlineStr">
         <is>
           <t>Acuan ISO/IEC 27001:2022</t>
         </is>
@@ -792,9 +867,12 @@
           <t>Klausul 9.1</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="28">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="C13" s="55" t="n"/>
+      <c r="D13" s="55" t="n"/>
+      <c r="E13" s="55" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1" s="28">
+      <c r="A14" s="53" t="inlineStr">
         <is>
           <t>Masa simpan record</t>
         </is>
@@ -804,28 +882,45 @@
           <t>3 tahun</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="23.85" customHeight="1" s="28">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="C14" s="55" t="n"/>
+      <c r="D14" s="55" t="n"/>
+      <c r="E14" s="55" t="n"/>
+    </row>
+    <row r="15" ht="43.5" customHeight="1" s="28">
+      <c r="A15" s="53" t="inlineStr">
         <is>
           <t>Tujuan</t>
         </is>
       </c>
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>Laporan bulanan KPI dan kinerja Divisi Operation, masukan pemantauan klausul 9.1 dan tinjauan manajemen klausul 9.3.2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="28">
-      <c r="A17" s="33" t="inlineStr">
+          <t>Laporan bulanan KPI dan kinerja Divisi Operation, sebagai masukan pemantauan (klausul 9.1) dan Management Review (klausul 9.3.2).</t>
+        </is>
+      </c>
+      <c r="C15" s="55" t="n"/>
+      <c r="D15" s="55" t="n"/>
+      <c r="E15" s="55" t="n"/>
+    </row>
+    <row r="16" s="28">
+      <c r="A16" s="55" t="n"/>
+      <c r="B16" s="55" t="n"/>
+      <c r="C16" s="55" t="n"/>
+      <c r="D16" s="55" t="n"/>
+      <c r="E16" s="55" t="n"/>
+    </row>
+    <row r="17" ht="16.5" customHeight="1" s="28">
+      <c r="A17" s="56" t="inlineStr">
         <is>
           <t>Cara pakai</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="28">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="B17" s="55" t="n"/>
+      <c r="C17" s="55" t="n"/>
+      <c r="D17" s="55" t="n"/>
+      <c r="E17" s="55" t="n"/>
+    </row>
+    <row r="18" ht="16.5" customHeight="1" s="28">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
@@ -835,121 +930,167 @@
           <t>Isi tahun di sheet KPI sel B3.</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="23.85" customHeight="1" s="28">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="C18" s="55" t="n"/>
+      <c r="D18" s="55" t="n"/>
+      <c r="E18" s="55" t="n"/>
+    </row>
+    <row r="19" ht="43.5" customHeight="1" s="28">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Setiap awal bulan, isi nilai aktual bulan sebelumnya dari sumber data di kolom Sumber. Persentase ditulis sebagai pecahan (0.95 = 95%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="23.85" customHeight="1" s="28">
-      <c r="A20" s="34" t="inlineStr">
+          <t>Setiap awal bulan, isi nilai aktual bulan sebelumnya dari sumber data di kolom Sumber. Tulis persentase sebagai pecahan (0.95 = 95%).</t>
+        </is>
+      </c>
+      <c r="C19" s="55" t="n"/>
+      <c r="D19" s="55" t="n"/>
+      <c r="E19" s="55" t="n"/>
+    </row>
+    <row r="20" ht="43.5" customHeight="1" s="28">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Status bulan terakhir dan rata-rata tahun berjalan dihitung otomatis; sel bulan merah berarti di bawah target.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="23.85" customHeight="1" s="28">
-      <c r="A21" s="34" t="inlineStr">
+          <t>Status bulan terakhir dan rata-rata tahun berjalan dihitung otomatis. Sel bulan berwarna merah berarti nilainya di bawah target.</t>
+        </is>
+      </c>
+      <c r="C20" s="55" t="n"/>
+      <c r="D20" s="55" t="n"/>
+      <c r="E20" s="55" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1" s="28">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Isi sheet Narasi Bulanan sebagai ringkasan untuk Direktur (COO) dan bahan tinjauan manajemen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="28">
-      <c r="A22" s="34" t="inlineStr">
+          <t>Isi sheet Narasi Bulanan sebagai ringkasan untuk Direktur (COO) dan bahan Management Review.</t>
+        </is>
+      </c>
+      <c r="C21" s="55" t="n"/>
+      <c r="D21" s="55" t="n"/>
+      <c r="E21" s="55" t="n"/>
+    </row>
+    <row r="22" ht="30" customHeight="1" s="28">
+      <c r="A22" s="35" t="inlineStr">
         <is>
           <t>5.</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Target adalah target awal dan dikalibrasi setelah 3 bulan data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="28">
-      <c r="A24" s="33" t="inlineStr">
+          <t>Target saat ini adalah target awal dan dikalibrasi setelah data 3 bulan terkumpul.</t>
+        </is>
+      </c>
+      <c r="C22" s="55" t="n"/>
+      <c r="D22" s="55" t="n"/>
+      <c r="E22" s="55" t="n"/>
+    </row>
+    <row r="23" s="28">
+      <c r="A23" s="55" t="n"/>
+      <c r="B23" s="55" t="n"/>
+      <c r="C23" s="55" t="n"/>
+      <c r="D23" s="55" t="n"/>
+      <c r="E23" s="55" t="n"/>
+    </row>
+    <row r="24" ht="16.5" customHeight="1" s="28">
+      <c r="A24" s="56" t="inlineStr">
         <is>
           <t>Legenda warna</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="28">
-      <c r="A25" s="36" t="n"/>
-      <c r="B25" s="34" t="inlineStr">
+      <c r="B24" s="55" t="n"/>
+      <c r="C24" s="55" t="n"/>
+      <c r="D24" s="55" t="n"/>
+      <c r="E24" s="55" t="n"/>
+    </row>
+    <row r="25" ht="16.5" customHeight="1" s="28">
+      <c r="A25" s="54" t="n"/>
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>Sel input: diisi pengguna</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="28">
-      <c r="A26" s="37" t="n"/>
-      <c r="B26" s="34" t="inlineStr">
+      <c r="C25" s="55" t="n"/>
+      <c r="D25" s="55" t="n"/>
+      <c r="E25" s="55" t="n"/>
+    </row>
+    <row r="26" ht="16.5" customHeight="1" s="28">
+      <c r="A26" s="57" t="n"/>
+      <c r="B26" s="35" t="inlineStr">
         <is>
           <t>Biru muda: tidak dipakai, tidak ada baris contoh</t>
         </is>
       </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="28">
-      <c r="A27" s="38" t="n"/>
-      <c r="B27" s="34" t="inlineStr">
+      <c r="C26" s="55" t="n"/>
+      <c r="D26" s="55" t="n"/>
+      <c r="E26" s="55" t="n"/>
+    </row>
+    <row r="27" ht="16.5" customHeight="1" s="28">
+      <c r="A27" s="58" t="n"/>
+      <c r="B27" s="35" t="inlineStr">
         <is>
           <t>Sel rumus: jangan diubah</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="28">
-      <c r="A29" s="33" t="inlineStr">
+      <c r="C27" s="55" t="n"/>
+      <c r="D27" s="55" t="n"/>
+      <c r="E27" s="55" t="n"/>
+    </row>
+    <row r="28" s="28">
+      <c r="A28" s="55" t="n"/>
+      <c r="B28" s="55" t="n"/>
+      <c r="C28" s="55" t="n"/>
+      <c r="D28" s="55" t="n"/>
+      <c r="E28" s="55" t="n"/>
+    </row>
+    <row r="29" ht="16.5" customHeight="1" s="28">
+      <c r="A29" s="56" t="inlineStr">
         <is>
           <t>Riwayat revisi</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="28">
-      <c r="A30" s="39" t="inlineStr">
+      <c r="B29" s="55" t="n"/>
+      <c r="C29" s="55" t="n"/>
+      <c r="D29" s="55" t="n"/>
+      <c r="E29" s="55" t="n"/>
+    </row>
+    <row r="30" ht="16.5" customHeight="1" s="28">
+      <c r="A30" s="59" t="inlineStr">
         <is>
           <t>Revisi</t>
         </is>
       </c>
-      <c r="B30" s="39" t="inlineStr">
+      <c r="B30" s="59" t="inlineStr">
         <is>
           <t>Tanggal</t>
         </is>
       </c>
-      <c r="C30" s="39" t="inlineStr">
+      <c r="C30" s="59" t="inlineStr">
         <is>
           <t>Uraian perubahan</t>
         </is>
       </c>
-      <c r="D30" s="39" t="inlineStr">
+      <c r="D30" s="59" t="inlineStr">
         <is>
           <t>Disusun</t>
         </is>
       </c>
-      <c r="E30" s="39" t="inlineStr">
+      <c r="E30" s="59" t="inlineStr">
         <is>
           <t>Disetujui</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="23.85" customHeight="1" s="28">
+    <row r="31" ht="30" customHeight="1" s="28">
       <c r="A31" s="32" t="inlineStr">
         <is>
           <t>00</t>
@@ -983,76 +1124,91 @@
       <c r="D32" s="32" t="n"/>
       <c r="E32" s="32" t="n"/>
     </row>
-    <row r="34" ht="15" customHeight="1" s="28">
-      <c r="A34" s="33" t="inlineStr">
+    <row r="33" s="28">
+      <c r="A33" s="55" t="n"/>
+      <c r="B33" s="55" t="n"/>
+      <c r="C33" s="55" t="n"/>
+      <c r="D33" s="55" t="n"/>
+      <c r="E33" s="55" t="n"/>
+    </row>
+    <row r="34" ht="16.5" customHeight="1" s="28">
+      <c r="A34" s="56" t="inlineStr">
         <is>
           <t>Pengesahan</t>
         </is>
       </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="28">
-      <c r="A35" s="39" t="inlineStr">
+      <c r="B34" s="55" t="n"/>
+      <c r="C34" s="55" t="n"/>
+      <c r="D34" s="55" t="n"/>
+      <c r="E34" s="55" t="n"/>
+    </row>
+    <row r="35" ht="16.5" customHeight="1" s="28">
+      <c r="A35" s="59" t="inlineStr">
         <is>
           <t>Peran</t>
         </is>
       </c>
-      <c r="B35" s="39" t="inlineStr">
+      <c r="B35" s="59" t="inlineStr">
         <is>
           <t>Nama dan jabatan</t>
         </is>
       </c>
-      <c r="C35" s="39" t="inlineStr">
+      <c r="C35" s="59" t="inlineStr">
         <is>
           <t>Tanda tangan</t>
         </is>
       </c>
-      <c r="D35" s="39" t="inlineStr">
+      <c r="D35" s="59" t="inlineStr">
         <is>
           <t>Tanggal</t>
         </is>
       </c>
+      <c r="E35" s="55" t="n"/>
     </row>
     <row r="36" ht="27.75" customHeight="1" s="28">
-      <c r="A36" s="40" t="inlineStr">
+      <c r="A36" s="32" t="inlineStr">
         <is>
           <t>Disusun oleh</t>
         </is>
       </c>
-      <c r="B36" s="40" t="inlineStr">
+      <c r="B36" s="32" t="inlineStr">
         <is>
           <t>Erik Dwi Yanto / Technical/Operation Engineer L1</t>
         </is>
       </c>
-      <c r="C36" s="40" t="n"/>
-      <c r="D36" s="40" t="n"/>
+      <c r="C36" s="32" t="n"/>
+      <c r="D36" s="32" t="n"/>
+      <c r="E36" s="55" t="n"/>
     </row>
     <row r="37" ht="27.75" customHeight="1" s="28">
-      <c r="A37" s="40" t="inlineStr">
+      <c r="A37" s="32" t="inlineStr">
         <is>
           <t>Diperiksa oleh</t>
         </is>
       </c>
-      <c r="B37" s="40" t="inlineStr">
+      <c r="B37" s="32" t="inlineStr">
         <is>
           <t>Fani Fatullah / VP Tech Operation and Services</t>
         </is>
       </c>
-      <c r="C37" s="40" t="n"/>
-      <c r="D37" s="40" t="n"/>
+      <c r="C37" s="32" t="n"/>
+      <c r="D37" s="32" t="n"/>
+      <c r="E37" s="55" t="n"/>
     </row>
     <row r="38" ht="27.75" customHeight="1" s="28">
-      <c r="A38" s="40" t="inlineStr">
+      <c r="A38" s="32" t="inlineStr">
         <is>
           <t>Disetujui oleh</t>
         </is>
       </c>
-      <c r="B38" s="40" t="inlineStr">
+      <c r="B38" s="32" t="inlineStr">
         <is>
           <t>Samuel Kristanto Utomo / President Director</t>
         </is>
       </c>
-      <c r="C38" s="40" t="n"/>
-      <c r="D38" s="40" t="n"/>
+      <c r="C38" s="32" t="n"/>
+      <c r="D38" s="32" t="n"/>
+      <c r="E38" s="55" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -1096,7 +1252,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -1104,11 +1260,23 @@
     <col width="4" customWidth="1" style="27" min="1" max="1"/>
     <col width="10" customWidth="1" style="27" min="2" max="2"/>
     <col width="36" customWidth="1" style="27" min="3" max="3"/>
-    <col width="6" customWidth="1" style="27" min="4" max="4"/>
-    <col width="8" customWidth="1" style="27" min="5" max="5"/>
+    <col width="7" customWidth="1" style="27" min="4" max="4"/>
+    <col width="10" customWidth="1" style="27" min="5" max="5"/>
     <col width="18" customWidth="1" style="27" min="6" max="6"/>
     <col width="7" customWidth="1" style="27" min="7" max="18"/>
-    <col width="10" customWidth="1" style="27" min="19" max="20"/>
+    <col width="13" customWidth="1" style="28" min="8" max="8"/>
+    <col width="13" customWidth="1" style="28" min="9" max="9"/>
+    <col width="13" customWidth="1" style="28" min="10" max="10"/>
+    <col width="13" customWidth="1" style="28" min="11" max="11"/>
+    <col width="13" customWidth="1" style="28" min="12" max="12"/>
+    <col width="13" customWidth="1" style="28" min="13" max="13"/>
+    <col width="13" customWidth="1" style="28" min="14" max="14"/>
+    <col width="13" customWidth="1" style="28" min="15" max="15"/>
+    <col width="13" customWidth="1" style="28" min="16" max="16"/>
+    <col width="13" customWidth="1" style="28" min="17" max="17"/>
+    <col width="13" customWidth="1" style="28" min="18" max="18"/>
+    <col width="14" customWidth="1" style="27" min="19" max="20"/>
+    <col width="13" customWidth="1" style="28" min="20" max="20"/>
     <col width="14" customWidth="1" style="27" min="21" max="21"/>
   </cols>
   <sheetData>
@@ -1129,7 +1297,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="5" ht="23.85" customHeight="1" s="28">
+    <row r="5" ht="30" customHeight="1" s="28">
       <c r="A5" s="43" t="inlineStr">
         <is>
           <t>No</t>
@@ -1236,7 +1404,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="28">
+    <row r="6" ht="27.3" customHeight="1" s="28">
       <c r="A6" s="44" t="n">
         <v>1</v>
       </c>
@@ -1263,32 +1431,32 @@
           <t>SNX-OPS-FRM-09</t>
         </is>
       </c>
-      <c r="G6" s="46" t="n"/>
-      <c r="H6" s="46" t="n"/>
-      <c r="I6" s="46" t="n"/>
-      <c r="J6" s="46" t="n"/>
-      <c r="K6" s="46" t="n"/>
-      <c r="L6" s="46" t="n"/>
-      <c r="M6" s="46" t="n"/>
-      <c r="N6" s="46" t="n"/>
-      <c r="O6" s="46" t="n"/>
-      <c r="P6" s="46" t="n"/>
-      <c r="Q6" s="46" t="n"/>
-      <c r="R6" s="46" t="n"/>
-      <c r="S6" s="47">
+      <c r="G6" s="60" t="n"/>
+      <c r="H6" s="60" t="n"/>
+      <c r="I6" s="60" t="n"/>
+      <c r="J6" s="60" t="n"/>
+      <c r="K6" s="60" t="n"/>
+      <c r="L6" s="60" t="n"/>
+      <c r="M6" s="60" t="n"/>
+      <c r="N6" s="60" t="n"/>
+      <c r="O6" s="60" t="n"/>
+      <c r="P6" s="60" t="n"/>
+      <c r="Q6" s="60" t="n"/>
+      <c r="R6" s="60" t="n"/>
+      <c r="S6" s="61">
         <f>IF(COUNT(G6:R6)=0,"",AVERAGE(G6:R6))</f>
         <v/>
       </c>
-      <c r="T6" s="47">
+      <c r="T6" s="61">
         <f>IF(COUNT(G6:R6)=0,"",LOOKUP(2,1/(G6:R6&lt;&gt;""),G6:R6))</f>
         <v/>
       </c>
-      <c r="U6" s="48">
+      <c r="U6" s="62">
         <f>IF(T6="","Belum diukur",IF(D6="≥",IF(T6&gt;=E6,"Tercapai","Di bawah target"),IF(T6&lt;=E6,"Tercapai","Di bawah target")))</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="28">
+    <row r="7" ht="27.3" customHeight="1" s="28">
       <c r="A7" s="44" t="n">
         <v>2</v>
       </c>
@@ -1315,32 +1483,32 @@
           <t>SNX-OPS-FRM-08</t>
         </is>
       </c>
-      <c r="G7" s="46" t="n"/>
-      <c r="H7" s="46" t="n"/>
-      <c r="I7" s="46" t="n"/>
-      <c r="J7" s="46" t="n"/>
-      <c r="K7" s="46" t="n"/>
-      <c r="L7" s="46" t="n"/>
-      <c r="M7" s="46" t="n"/>
-      <c r="N7" s="46" t="n"/>
-      <c r="O7" s="46" t="n"/>
-      <c r="P7" s="46" t="n"/>
-      <c r="Q7" s="46" t="n"/>
-      <c r="R7" s="46" t="n"/>
-      <c r="S7" s="47">
+      <c r="G7" s="60" t="n"/>
+      <c r="H7" s="60" t="n"/>
+      <c r="I7" s="60" t="n"/>
+      <c r="J7" s="60" t="n"/>
+      <c r="K7" s="60" t="n"/>
+      <c r="L7" s="60" t="n"/>
+      <c r="M7" s="60" t="n"/>
+      <c r="N7" s="60" t="n"/>
+      <c r="O7" s="60" t="n"/>
+      <c r="P7" s="60" t="n"/>
+      <c r="Q7" s="60" t="n"/>
+      <c r="R7" s="60" t="n"/>
+      <c r="S7" s="61">
         <f>IF(COUNT(G7:R7)=0,"",AVERAGE(G7:R7))</f>
         <v/>
       </c>
-      <c r="T7" s="47">
+      <c r="T7" s="61">
         <f>IF(COUNT(G7:R7)=0,"",LOOKUP(2,1/(G7:R7&lt;&gt;""),G7:R7))</f>
         <v/>
       </c>
-      <c r="U7" s="48">
+      <c r="U7" s="62">
         <f>IF(T7="","Belum diukur",IF(D7="≥",IF(T7&gt;=E7,"Tercapai","Di bawah target"),IF(T7&lt;=E7,"Tercapai","Di bawah target")))</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="28">
+    <row r="8" ht="15.2" customHeight="1" s="28">
       <c r="A8" s="44" t="n">
         <v>3</v>
       </c>
@@ -1367,32 +1535,32 @@
           <t>SNX-ISMS-FRM-01</t>
         </is>
       </c>
-      <c r="G8" s="46" t="n"/>
-      <c r="H8" s="46" t="n"/>
-      <c r="I8" s="46" t="n"/>
-      <c r="J8" s="46" t="n"/>
-      <c r="K8" s="46" t="n"/>
-      <c r="L8" s="46" t="n"/>
-      <c r="M8" s="46" t="n"/>
-      <c r="N8" s="46" t="n"/>
-      <c r="O8" s="46" t="n"/>
-      <c r="P8" s="46" t="n"/>
-      <c r="Q8" s="46" t="n"/>
-      <c r="R8" s="46" t="n"/>
-      <c r="S8" s="47">
+      <c r="G8" s="60" t="n"/>
+      <c r="H8" s="60" t="n"/>
+      <c r="I8" s="60" t="n"/>
+      <c r="J8" s="60" t="n"/>
+      <c r="K8" s="60" t="n"/>
+      <c r="L8" s="60" t="n"/>
+      <c r="M8" s="60" t="n"/>
+      <c r="N8" s="60" t="n"/>
+      <c r="O8" s="60" t="n"/>
+      <c r="P8" s="60" t="n"/>
+      <c r="Q8" s="60" t="n"/>
+      <c r="R8" s="60" t="n"/>
+      <c r="S8" s="61">
         <f>IF(COUNT(G8:R8)=0,"",AVERAGE(G8:R8))</f>
         <v/>
       </c>
-      <c r="T8" s="47">
+      <c r="T8" s="61">
         <f>IF(COUNT(G8:R8)=0,"",LOOKUP(2,1/(G8:R8&lt;&gt;""),G8:R8))</f>
         <v/>
       </c>
-      <c r="U8" s="48">
+      <c r="U8" s="62">
         <f>IF(T8="","Belum diukur",IF(D8="≥",IF(T8&gt;=E8,"Tercapai","Di bawah target"),IF(T8&lt;=E8,"Tercapai","Di bawah target")))</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="28">
+    <row r="9" ht="15.2" customHeight="1" s="28">
       <c r="A9" s="44" t="n">
         <v>4</v>
       </c>
@@ -1419,32 +1587,32 @@
           <t>SNX-ISMS-FRM-01</t>
         </is>
       </c>
-      <c r="G9" s="46" t="n"/>
-      <c r="H9" s="46" t="n"/>
-      <c r="I9" s="46" t="n"/>
-      <c r="J9" s="46" t="n"/>
-      <c r="K9" s="46" t="n"/>
-      <c r="L9" s="46" t="n"/>
-      <c r="M9" s="46" t="n"/>
-      <c r="N9" s="46" t="n"/>
-      <c r="O9" s="46" t="n"/>
-      <c r="P9" s="46" t="n"/>
-      <c r="Q9" s="46" t="n"/>
-      <c r="R9" s="46" t="n"/>
-      <c r="S9" s="47">
+      <c r="G9" s="60" t="n"/>
+      <c r="H9" s="60" t="n"/>
+      <c r="I9" s="60" t="n"/>
+      <c r="J9" s="60" t="n"/>
+      <c r="K9" s="60" t="n"/>
+      <c r="L9" s="60" t="n"/>
+      <c r="M9" s="60" t="n"/>
+      <c r="N9" s="60" t="n"/>
+      <c r="O9" s="60" t="n"/>
+      <c r="P9" s="60" t="n"/>
+      <c r="Q9" s="60" t="n"/>
+      <c r="R9" s="60" t="n"/>
+      <c r="S9" s="61">
         <f>IF(COUNT(G9:R9)=0,"",AVERAGE(G9:R9))</f>
         <v/>
       </c>
-      <c r="T9" s="47">
+      <c r="T9" s="61">
         <f>IF(COUNT(G9:R9)=0,"",LOOKUP(2,1/(G9:R9&lt;&gt;""),G9:R9))</f>
         <v/>
       </c>
-      <c r="U9" s="48">
+      <c r="U9" s="62">
         <f>IF(T9="","Belum diukur",IF(D9="≥",IF(T9&gt;=E9,"Tercapai","Di bawah target"),IF(T9&lt;=E9,"Tercapai","Di bawah target")))</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="28">
+    <row r="10" ht="27.3" customHeight="1" s="28">
       <c r="A10" s="44" t="n">
         <v>5</v>
       </c>
@@ -1471,32 +1639,32 @@
           <t>SNX-OPS-FRM-07</t>
         </is>
       </c>
-      <c r="G10" s="46" t="n"/>
-      <c r="H10" s="46" t="n"/>
-      <c r="I10" s="46" t="n"/>
-      <c r="J10" s="46" t="n"/>
-      <c r="K10" s="46" t="n"/>
-      <c r="L10" s="46" t="n"/>
-      <c r="M10" s="46" t="n"/>
-      <c r="N10" s="46" t="n"/>
-      <c r="O10" s="46" t="n"/>
-      <c r="P10" s="46" t="n"/>
-      <c r="Q10" s="46" t="n"/>
-      <c r="R10" s="46" t="n"/>
-      <c r="S10" s="47">
+      <c r="G10" s="60" t="n"/>
+      <c r="H10" s="60" t="n"/>
+      <c r="I10" s="60" t="n"/>
+      <c r="J10" s="60" t="n"/>
+      <c r="K10" s="60" t="n"/>
+      <c r="L10" s="60" t="n"/>
+      <c r="M10" s="60" t="n"/>
+      <c r="N10" s="60" t="n"/>
+      <c r="O10" s="60" t="n"/>
+      <c r="P10" s="60" t="n"/>
+      <c r="Q10" s="60" t="n"/>
+      <c r="R10" s="60" t="n"/>
+      <c r="S10" s="61">
         <f>IF(COUNT(G10:R10)=0,"",AVERAGE(G10:R10))</f>
         <v/>
       </c>
-      <c r="T10" s="47">
+      <c r="T10" s="61">
         <f>IF(COUNT(G10:R10)=0,"",LOOKUP(2,1/(G10:R10&lt;&gt;""),G10:R10))</f>
         <v/>
       </c>
-      <c r="U10" s="48">
+      <c r="U10" s="62">
         <f>IF(T10="","Belum diukur",IF(D10="≥",IF(T10&gt;=E10,"Tercapai","Di bawah target"),IF(T10&lt;=E10,"Tercapai","Di bawah target")))</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="28">
+    <row r="11" ht="15.2" customHeight="1" s="28">
       <c r="A11" s="44" t="n">
         <v>6</v>
       </c>
@@ -1523,32 +1691,32 @@
           <t>SNX-OPS-FRM-04</t>
         </is>
       </c>
-      <c r="G11" s="46" t="n"/>
-      <c r="H11" s="46" t="n"/>
-      <c r="I11" s="46" t="n"/>
-      <c r="J11" s="46" t="n"/>
-      <c r="K11" s="46" t="n"/>
-      <c r="L11" s="46" t="n"/>
-      <c r="M11" s="46" t="n"/>
-      <c r="N11" s="46" t="n"/>
-      <c r="O11" s="46" t="n"/>
-      <c r="P11" s="46" t="n"/>
-      <c r="Q11" s="46" t="n"/>
-      <c r="R11" s="46" t="n"/>
-      <c r="S11" s="47">
+      <c r="G11" s="60" t="n"/>
+      <c r="H11" s="60" t="n"/>
+      <c r="I11" s="60" t="n"/>
+      <c r="J11" s="60" t="n"/>
+      <c r="K11" s="60" t="n"/>
+      <c r="L11" s="60" t="n"/>
+      <c r="M11" s="60" t="n"/>
+      <c r="N11" s="60" t="n"/>
+      <c r="O11" s="60" t="n"/>
+      <c r="P11" s="60" t="n"/>
+      <c r="Q11" s="60" t="n"/>
+      <c r="R11" s="60" t="n"/>
+      <c r="S11" s="61">
         <f>IF(COUNT(G11:R11)=0,"",AVERAGE(G11:R11))</f>
         <v/>
       </c>
-      <c r="T11" s="47">
+      <c r="T11" s="61">
         <f>IF(COUNT(G11:R11)=0,"",LOOKUP(2,1/(G11:R11&lt;&gt;""),G11:R11))</f>
         <v/>
       </c>
-      <c r="U11" s="48">
+      <c r="U11" s="62">
         <f>IF(T11="","Belum diukur",IF(D11="≥",IF(T11&gt;=E11,"Tercapai","Di bawah target"),IF(T11&lt;=E11,"Tercapai","Di bawah target")))</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="22.35" customHeight="1" s="28">
+    <row r="12" ht="27.3" customHeight="1" s="28">
       <c r="A12" s="44" t="n">
         <v>7</v>
       </c>
@@ -1575,32 +1743,32 @@
           <t>SIEM, SNX-ISMS-FRM-02</t>
         </is>
       </c>
-      <c r="G12" s="46" t="n"/>
-      <c r="H12" s="46" t="n"/>
-      <c r="I12" s="46" t="n"/>
-      <c r="J12" s="46" t="n"/>
-      <c r="K12" s="46" t="n"/>
-      <c r="L12" s="46" t="n"/>
-      <c r="M12" s="46" t="n"/>
-      <c r="N12" s="46" t="n"/>
-      <c r="O12" s="46" t="n"/>
-      <c r="P12" s="46" t="n"/>
-      <c r="Q12" s="46" t="n"/>
-      <c r="R12" s="46" t="n"/>
-      <c r="S12" s="47">
+      <c r="G12" s="60" t="n"/>
+      <c r="H12" s="60" t="n"/>
+      <c r="I12" s="60" t="n"/>
+      <c r="J12" s="60" t="n"/>
+      <c r="K12" s="60" t="n"/>
+      <c r="L12" s="60" t="n"/>
+      <c r="M12" s="60" t="n"/>
+      <c r="N12" s="60" t="n"/>
+      <c r="O12" s="60" t="n"/>
+      <c r="P12" s="60" t="n"/>
+      <c r="Q12" s="60" t="n"/>
+      <c r="R12" s="60" t="n"/>
+      <c r="S12" s="61">
         <f>IF(COUNT(G12:R12)=0,"",AVERAGE(G12:R12))</f>
         <v/>
       </c>
-      <c r="T12" s="47">
+      <c r="T12" s="61">
         <f>IF(COUNT(G12:R12)=0,"",LOOKUP(2,1/(G12:R12&lt;&gt;""),G12:R12))</f>
         <v/>
       </c>
-      <c r="U12" s="48">
+      <c r="U12" s="62">
         <f>IF(T12="","Belum diukur",IF(D12="≥",IF(T12&gt;=E12,"Tercapai","Di bawah target"),IF(T12&lt;=E12,"Tercapai","Di bawah target")))</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="22.35" customHeight="1" s="28">
+    <row r="13" ht="27.3" customHeight="1" s="28">
       <c r="A13" s="44" t="n">
         <v>8</v>
       </c>
@@ -1627,32 +1795,32 @@
           <t>Tiket vulnerability</t>
         </is>
       </c>
-      <c r="G13" s="46" t="n"/>
-      <c r="H13" s="46" t="n"/>
-      <c r="I13" s="46" t="n"/>
-      <c r="J13" s="46" t="n"/>
-      <c r="K13" s="46" t="n"/>
-      <c r="L13" s="46" t="n"/>
-      <c r="M13" s="46" t="n"/>
-      <c r="N13" s="46" t="n"/>
-      <c r="O13" s="46" t="n"/>
-      <c r="P13" s="46" t="n"/>
-      <c r="Q13" s="46" t="n"/>
-      <c r="R13" s="46" t="n"/>
-      <c r="S13" s="47">
+      <c r="G13" s="60" t="n"/>
+      <c r="H13" s="60" t="n"/>
+      <c r="I13" s="60" t="n"/>
+      <c r="J13" s="60" t="n"/>
+      <c r="K13" s="60" t="n"/>
+      <c r="L13" s="60" t="n"/>
+      <c r="M13" s="60" t="n"/>
+      <c r="N13" s="60" t="n"/>
+      <c r="O13" s="60" t="n"/>
+      <c r="P13" s="60" t="n"/>
+      <c r="Q13" s="60" t="n"/>
+      <c r="R13" s="60" t="n"/>
+      <c r="S13" s="61">
         <f>IF(COUNT(G13:R13)=0,"",AVERAGE(G13:R13))</f>
         <v/>
       </c>
-      <c r="T13" s="47">
+      <c r="T13" s="61">
         <f>IF(COUNT(G13:R13)=0,"",LOOKUP(2,1/(G13:R13&lt;&gt;""),G13:R13))</f>
         <v/>
       </c>
-      <c r="U13" s="48">
+      <c r="U13" s="62">
         <f>IF(T13="","Belum diukur",IF(D13="≥",IF(T13&gt;=E13,"Tercapai","Di bawah target"),IF(T13&lt;=E13,"Tercapai","Di bawah target")))</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="28">
+    <row r="14" ht="27.3" customHeight="1" s="28">
       <c r="A14" s="44" t="n">
         <v>9</v>
       </c>
@@ -1679,32 +1847,32 @@
           <t>SNX-ISMS-FRM-02</t>
         </is>
       </c>
-      <c r="G14" s="46" t="n"/>
-      <c r="H14" s="46" t="n"/>
-      <c r="I14" s="46" t="n"/>
-      <c r="J14" s="46" t="n"/>
-      <c r="K14" s="46" t="n"/>
-      <c r="L14" s="46" t="n"/>
-      <c r="M14" s="46" t="n"/>
-      <c r="N14" s="46" t="n"/>
-      <c r="O14" s="46" t="n"/>
-      <c r="P14" s="46" t="n"/>
-      <c r="Q14" s="46" t="n"/>
-      <c r="R14" s="46" t="n"/>
-      <c r="S14" s="47">
+      <c r="G14" s="60" t="n"/>
+      <c r="H14" s="60" t="n"/>
+      <c r="I14" s="60" t="n"/>
+      <c r="J14" s="60" t="n"/>
+      <c r="K14" s="60" t="n"/>
+      <c r="L14" s="60" t="n"/>
+      <c r="M14" s="60" t="n"/>
+      <c r="N14" s="60" t="n"/>
+      <c r="O14" s="60" t="n"/>
+      <c r="P14" s="60" t="n"/>
+      <c r="Q14" s="60" t="n"/>
+      <c r="R14" s="60" t="n"/>
+      <c r="S14" s="61">
         <f>IF(COUNT(G14:R14)=0,"",AVERAGE(G14:R14))</f>
         <v/>
       </c>
-      <c r="T14" s="47">
+      <c r="T14" s="61">
         <f>IF(COUNT(G14:R14)=0,"",LOOKUP(2,1/(G14:R14&lt;&gt;""),G14:R14))</f>
         <v/>
       </c>
-      <c r="U14" s="48">
+      <c r="U14" s="62">
         <f>IF(T14="","Belum diukur",IF(D14="≥",IF(T14&gt;=E14,"Tercapai","Di bawah target"),IF(T14&lt;=E14,"Tercapai","Di bawah target")))</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="28">
+    <row r="15" ht="27.3" customHeight="1" s="28">
       <c r="A15" s="44" t="n">
         <v>10</v>
       </c>
@@ -1731,32 +1899,32 @@
           <t>SNX-ISMS-FRM-02</t>
         </is>
       </c>
-      <c r="G15" s="50" t="n"/>
-      <c r="H15" s="50" t="n"/>
-      <c r="I15" s="50" t="n"/>
-      <c r="J15" s="50" t="n"/>
-      <c r="K15" s="50" t="n"/>
-      <c r="L15" s="50" t="n"/>
-      <c r="M15" s="50" t="n"/>
-      <c r="N15" s="50" t="n"/>
-      <c r="O15" s="50" t="n"/>
-      <c r="P15" s="50" t="n"/>
-      <c r="Q15" s="50" t="n"/>
-      <c r="R15" s="50" t="n"/>
-      <c r="S15" s="51">
+      <c r="G15" s="63" t="n"/>
+      <c r="H15" s="63" t="n"/>
+      <c r="I15" s="63" t="n"/>
+      <c r="J15" s="63" t="n"/>
+      <c r="K15" s="63" t="n"/>
+      <c r="L15" s="63" t="n"/>
+      <c r="M15" s="63" t="n"/>
+      <c r="N15" s="63" t="n"/>
+      <c r="O15" s="63" t="n"/>
+      <c r="P15" s="63" t="n"/>
+      <c r="Q15" s="63" t="n"/>
+      <c r="R15" s="63" t="n"/>
+      <c r="S15" s="64">
         <f>IF(COUNT(G15:R15)=0,"",AVERAGE(G15:R15))</f>
         <v/>
       </c>
-      <c r="T15" s="51">
+      <c r="T15" s="64">
         <f>IF(COUNT(G15:R15)=0,"",LOOKUP(2,1/(G15:R15&lt;&gt;""),G15:R15))</f>
         <v/>
       </c>
-      <c r="U15" s="48">
+      <c r="U15" s="62">
         <f>IF(T15="","Belum diukur",IF(D15="≥",IF(T15&gt;=E15,"Tercapai","Di bawah target"),IF(T15&lt;=E15,"Tercapai","Di bawah target")))</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="28">
+    <row r="16" ht="27.3" customHeight="1" s="28">
       <c r="A16" s="44" t="n">
         <v>11</v>
       </c>
@@ -1783,32 +1951,32 @@
           <t>SNX-OPS-FRM-09</t>
         </is>
       </c>
-      <c r="G16" s="46" t="n"/>
-      <c r="H16" s="46" t="n"/>
-      <c r="I16" s="46" t="n"/>
-      <c r="J16" s="46" t="n"/>
-      <c r="K16" s="46" t="n"/>
-      <c r="L16" s="46" t="n"/>
-      <c r="M16" s="46" t="n"/>
-      <c r="N16" s="46" t="n"/>
-      <c r="O16" s="46" t="n"/>
-      <c r="P16" s="46" t="n"/>
-      <c r="Q16" s="46" t="n"/>
-      <c r="R16" s="46" t="n"/>
-      <c r="S16" s="47">
+      <c r="G16" s="60" t="n"/>
+      <c r="H16" s="60" t="n"/>
+      <c r="I16" s="60" t="n"/>
+      <c r="J16" s="60" t="n"/>
+      <c r="K16" s="60" t="n"/>
+      <c r="L16" s="60" t="n"/>
+      <c r="M16" s="60" t="n"/>
+      <c r="N16" s="60" t="n"/>
+      <c r="O16" s="60" t="n"/>
+      <c r="P16" s="60" t="n"/>
+      <c r="Q16" s="60" t="n"/>
+      <c r="R16" s="60" t="n"/>
+      <c r="S16" s="61">
         <f>IF(COUNT(G16:R16)=0,"",AVERAGE(G16:R16))</f>
         <v/>
       </c>
-      <c r="T16" s="47">
+      <c r="T16" s="61">
         <f>IF(COUNT(G16:R16)=0,"",LOOKUP(2,1/(G16:R16&lt;&gt;""),G16:R16))</f>
         <v/>
       </c>
-      <c r="U16" s="48">
+      <c r="U16" s="62">
         <f>IF(T16="","Belum diukur",IF(D16="≥",IF(T16&gt;=E16,"Tercapai","Di bawah target"),IF(T16&lt;=E16,"Tercapai","Di bawah target")))</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="28">
+    <row r="17" ht="27.3" customHeight="1" s="28">
       <c r="A17" s="44" t="n">
         <v>12</v>
       </c>
@@ -1835,32 +2003,32 @@
           <t>SNX-OPS-FRM-01</t>
         </is>
       </c>
-      <c r="G17" s="46" t="n"/>
-      <c r="H17" s="46" t="n"/>
-      <c r="I17" s="46" t="n"/>
-      <c r="J17" s="46" t="n"/>
-      <c r="K17" s="46" t="n"/>
-      <c r="L17" s="46" t="n"/>
-      <c r="M17" s="46" t="n"/>
-      <c r="N17" s="46" t="n"/>
-      <c r="O17" s="46" t="n"/>
-      <c r="P17" s="46" t="n"/>
-      <c r="Q17" s="46" t="n"/>
-      <c r="R17" s="46" t="n"/>
-      <c r="S17" s="47">
+      <c r="G17" s="60" t="n"/>
+      <c r="H17" s="60" t="n"/>
+      <c r="I17" s="60" t="n"/>
+      <c r="J17" s="60" t="n"/>
+      <c r="K17" s="60" t="n"/>
+      <c r="L17" s="60" t="n"/>
+      <c r="M17" s="60" t="n"/>
+      <c r="N17" s="60" t="n"/>
+      <c r="O17" s="60" t="n"/>
+      <c r="P17" s="60" t="n"/>
+      <c r="Q17" s="60" t="n"/>
+      <c r="R17" s="60" t="n"/>
+      <c r="S17" s="61">
         <f>IF(COUNT(G17:R17)=0,"",AVERAGE(G17:R17))</f>
         <v/>
       </c>
-      <c r="T17" s="47">
+      <c r="T17" s="61">
         <f>IF(COUNT(G17:R17)=0,"",LOOKUP(2,1/(G17:R17&lt;&gt;""),G17:R17))</f>
         <v/>
       </c>
-      <c r="U17" s="48">
+      <c r="U17" s="62">
         <f>IF(T17="","Belum diukur",IF(D17="≥",IF(T17&gt;=E17,"Tercapai","Di bawah target"),IF(T17&lt;=E17,"Tercapai","Di bawah target")))</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="28">
+    <row r="18" ht="27.3" customHeight="1" s="28">
       <c r="A18" s="44" t="n">
         <v>13</v>
       </c>
@@ -1887,32 +2055,32 @@
           <t>SNX-OPS-FRM-01</t>
         </is>
       </c>
-      <c r="G18" s="46" t="n"/>
-      <c r="H18" s="46" t="n"/>
-      <c r="I18" s="46" t="n"/>
-      <c r="J18" s="46" t="n"/>
-      <c r="K18" s="46" t="n"/>
-      <c r="L18" s="46" t="n"/>
-      <c r="M18" s="46" t="n"/>
-      <c r="N18" s="46" t="n"/>
-      <c r="O18" s="46" t="n"/>
-      <c r="P18" s="46" t="n"/>
-      <c r="Q18" s="46" t="n"/>
-      <c r="R18" s="46" t="n"/>
-      <c r="S18" s="47">
+      <c r="G18" s="60" t="n"/>
+      <c r="H18" s="60" t="n"/>
+      <c r="I18" s="60" t="n"/>
+      <c r="J18" s="60" t="n"/>
+      <c r="K18" s="60" t="n"/>
+      <c r="L18" s="60" t="n"/>
+      <c r="M18" s="60" t="n"/>
+      <c r="N18" s="60" t="n"/>
+      <c r="O18" s="60" t="n"/>
+      <c r="P18" s="60" t="n"/>
+      <c r="Q18" s="60" t="n"/>
+      <c r="R18" s="60" t="n"/>
+      <c r="S18" s="61">
         <f>IF(COUNT(G18:R18)=0,"",AVERAGE(G18:R18))</f>
         <v/>
       </c>
-      <c r="T18" s="47">
+      <c r="T18" s="61">
         <f>IF(COUNT(G18:R18)=0,"",LOOKUP(2,1/(G18:R18&lt;&gt;""),G18:R18))</f>
         <v/>
       </c>
-      <c r="U18" s="48">
+      <c r="U18" s="62">
         <f>IF(T18="","Belum diukur",IF(D18="≥",IF(T18&gt;=E18,"Tercapai","Di bawah target"),IF(T18&lt;=E18,"Tercapai","Di bawah target")))</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="28">
+    <row r="19" ht="27.3" customHeight="1" s="28">
       <c r="A19" s="44" t="n">
         <v>14</v>
       </c>
@@ -1939,32 +2107,32 @@
           <t>SNX-OPS-FRM-10</t>
         </is>
       </c>
-      <c r="G19" s="46" t="n"/>
-      <c r="H19" s="46" t="n"/>
-      <c r="I19" s="46" t="n"/>
-      <c r="J19" s="46" t="n"/>
-      <c r="K19" s="46" t="n"/>
-      <c r="L19" s="46" t="n"/>
-      <c r="M19" s="46" t="n"/>
-      <c r="N19" s="46" t="n"/>
-      <c r="O19" s="46" t="n"/>
-      <c r="P19" s="46" t="n"/>
-      <c r="Q19" s="46" t="n"/>
-      <c r="R19" s="46" t="n"/>
-      <c r="S19" s="47">
+      <c r="G19" s="60" t="n"/>
+      <c r="H19" s="60" t="n"/>
+      <c r="I19" s="60" t="n"/>
+      <c r="J19" s="60" t="n"/>
+      <c r="K19" s="60" t="n"/>
+      <c r="L19" s="60" t="n"/>
+      <c r="M19" s="60" t="n"/>
+      <c r="N19" s="60" t="n"/>
+      <c r="O19" s="60" t="n"/>
+      <c r="P19" s="60" t="n"/>
+      <c r="Q19" s="60" t="n"/>
+      <c r="R19" s="60" t="n"/>
+      <c r="S19" s="61">
         <f>IF(COUNT(G19:R19)=0,"",AVERAGE(G19:R19))</f>
         <v/>
       </c>
-      <c r="T19" s="47">
+      <c r="T19" s="61">
         <f>IF(COUNT(G19:R19)=0,"",LOOKUP(2,1/(G19:R19&lt;&gt;""),G19:R19))</f>
         <v/>
       </c>
-      <c r="U19" s="48">
+      <c r="U19" s="62">
         <f>IF(T19="","Belum diukur",IF(D19="≥",IF(T19&gt;=E19,"Tercapai","Di bawah target"),IF(T19&lt;=E19,"Tercapai","Di bawah target")))</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="28">
+    <row r="20" ht="27.3" customHeight="1" s="28">
       <c r="A20" s="44" t="n">
         <v>15</v>
       </c>
@@ -1991,32 +2159,32 @@
           <t>SNX-ISMS-REG-04</t>
         </is>
       </c>
-      <c r="G20" s="46" t="n"/>
-      <c r="H20" s="46" t="n"/>
-      <c r="I20" s="46" t="n"/>
-      <c r="J20" s="46" t="n"/>
-      <c r="K20" s="46" t="n"/>
-      <c r="L20" s="46" t="n"/>
-      <c r="M20" s="46" t="n"/>
-      <c r="N20" s="46" t="n"/>
-      <c r="O20" s="46" t="n"/>
-      <c r="P20" s="46" t="n"/>
-      <c r="Q20" s="46" t="n"/>
-      <c r="R20" s="46" t="n"/>
-      <c r="S20" s="47">
+      <c r="G20" s="60" t="n"/>
+      <c r="H20" s="60" t="n"/>
+      <c r="I20" s="60" t="n"/>
+      <c r="J20" s="60" t="n"/>
+      <c r="K20" s="60" t="n"/>
+      <c r="L20" s="60" t="n"/>
+      <c r="M20" s="60" t="n"/>
+      <c r="N20" s="60" t="n"/>
+      <c r="O20" s="60" t="n"/>
+      <c r="P20" s="60" t="n"/>
+      <c r="Q20" s="60" t="n"/>
+      <c r="R20" s="60" t="n"/>
+      <c r="S20" s="61">
         <f>IF(COUNT(G20:R20)=0,"",AVERAGE(G20:R20))</f>
         <v/>
       </c>
-      <c r="T20" s="47">
+      <c r="T20" s="61">
         <f>IF(COUNT(G20:R20)=0,"",LOOKUP(2,1/(G20:R20&lt;&gt;""),G20:R20))</f>
         <v/>
       </c>
-      <c r="U20" s="48">
+      <c r="U20" s="62">
         <f>IF(T20="","Belum diukur",IF(D20="≥",IF(T20&gt;=E20,"Tercapai","Di bawah target"),IF(T20&lt;=E20,"Tercapai","Di bawah target")))</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="28">
+    <row r="21" ht="27.3" customHeight="1" s="28">
       <c r="A21" s="44" t="n">
         <v>16</v>
       </c>
@@ -2043,32 +2211,32 @@
           <t>SNX-ISMS-REG-03</t>
         </is>
       </c>
-      <c r="G21" s="46" t="n"/>
-      <c r="H21" s="46" t="n"/>
-      <c r="I21" s="46" t="n"/>
-      <c r="J21" s="46" t="n"/>
-      <c r="K21" s="46" t="n"/>
-      <c r="L21" s="46" t="n"/>
-      <c r="M21" s="46" t="n"/>
-      <c r="N21" s="46" t="n"/>
-      <c r="O21" s="46" t="n"/>
-      <c r="P21" s="46" t="n"/>
-      <c r="Q21" s="46" t="n"/>
-      <c r="R21" s="46" t="n"/>
-      <c r="S21" s="47">
+      <c r="G21" s="60" t="n"/>
+      <c r="H21" s="60" t="n"/>
+      <c r="I21" s="60" t="n"/>
+      <c r="J21" s="60" t="n"/>
+      <c r="K21" s="60" t="n"/>
+      <c r="L21" s="60" t="n"/>
+      <c r="M21" s="60" t="n"/>
+      <c r="N21" s="60" t="n"/>
+      <c r="O21" s="60" t="n"/>
+      <c r="P21" s="60" t="n"/>
+      <c r="Q21" s="60" t="n"/>
+      <c r="R21" s="60" t="n"/>
+      <c r="S21" s="61">
         <f>IF(COUNT(G21:R21)=0,"",AVERAGE(G21:R21))</f>
         <v/>
       </c>
-      <c r="T21" s="47">
+      <c r="T21" s="61">
         <f>IF(COUNT(G21:R21)=0,"",LOOKUP(2,1/(G21:R21&lt;&gt;""),G21:R21))</f>
         <v/>
       </c>
-      <c r="U21" s="48">
+      <c r="U21" s="62">
         <f>IF(T21="","Belum diukur",IF(D21="≥",IF(T21&gt;=E21,"Tercapai","Di bawah target"),IF(T21&lt;=E21,"Tercapai","Di bawah target")))</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="28">
+    <row r="22" ht="27.3" customHeight="1" s="28">
       <c r="A22" s="44" t="n">
         <v>17</v>
       </c>
@@ -2095,38 +2263,80 @@
           <t>Shift Log</t>
         </is>
       </c>
-      <c r="G22" s="46" t="n"/>
-      <c r="H22" s="46" t="n"/>
-      <c r="I22" s="46" t="n"/>
-      <c r="J22" s="46" t="n"/>
-      <c r="K22" s="46" t="n"/>
-      <c r="L22" s="46" t="n"/>
-      <c r="M22" s="46" t="n"/>
-      <c r="N22" s="46" t="n"/>
-      <c r="O22" s="46" t="n"/>
-      <c r="P22" s="46" t="n"/>
-      <c r="Q22" s="46" t="n"/>
-      <c r="R22" s="46" t="n"/>
-      <c r="S22" s="47">
+      <c r="G22" s="60" t="n"/>
+      <c r="H22" s="60" t="n"/>
+      <c r="I22" s="60" t="n"/>
+      <c r="J22" s="60" t="n"/>
+      <c r="K22" s="60" t="n"/>
+      <c r="L22" s="60" t="n"/>
+      <c r="M22" s="60" t="n"/>
+      <c r="N22" s="60" t="n"/>
+      <c r="O22" s="60" t="n"/>
+      <c r="P22" s="60" t="n"/>
+      <c r="Q22" s="60" t="n"/>
+      <c r="R22" s="60" t="n"/>
+      <c r="S22" s="61">
         <f>IF(COUNT(G22:R22)=0,"",AVERAGE(G22:R22))</f>
         <v/>
       </c>
-      <c r="T22" s="47">
+      <c r="T22" s="61">
         <f>IF(COUNT(G22:R22)=0,"",LOOKUP(2,1/(G22:R22&lt;&gt;""),G22:R22))</f>
         <v/>
       </c>
-      <c r="U22" s="48">
+      <c r="U22" s="62">
         <f>IF(T22="","Belum diukur",IF(D22="≥",IF(T22&gt;=E22,"Tercapai","Di bawah target"),IF(T22&lt;=E22,"Tercapai","Di bawah target")))</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="28">
-      <c r="C24" s="52" t="inlineStr">
+    <row r="23" s="28">
+      <c r="A23" s="65" t="n"/>
+      <c r="B23" s="65" t="n"/>
+      <c r="C23" s="65" t="n"/>
+      <c r="D23" s="65" t="n"/>
+      <c r="E23" s="65" t="n"/>
+      <c r="F23" s="65" t="n"/>
+      <c r="G23" s="65" t="n"/>
+      <c r="H23" s="65" t="n"/>
+      <c r="I23" s="65" t="n"/>
+      <c r="J23" s="65" t="n"/>
+      <c r="K23" s="65" t="n"/>
+      <c r="L23" s="65" t="n"/>
+      <c r="M23" s="65" t="n"/>
+      <c r="N23" s="65" t="n"/>
+      <c r="O23" s="65" t="n"/>
+      <c r="P23" s="65" t="n"/>
+      <c r="Q23" s="65" t="n"/>
+      <c r="R23" s="65" t="n"/>
+      <c r="S23" s="65" t="n"/>
+      <c r="T23" s="65" t="n"/>
+      <c r="U23" s="65" t="n"/>
+    </row>
+    <row r="24" ht="30" customHeight="1" s="28">
+      <c r="A24" s="65" t="n"/>
+      <c r="B24" s="65" t="n"/>
+      <c r="C24" s="66" t="inlineStr">
         <is>
           <t>KPI tercapai (bulan terakhir)</t>
         </is>
       </c>
-      <c r="U24" s="27">
+      <c r="D24" s="65" t="n"/>
+      <c r="E24" s="65" t="n"/>
+      <c r="F24" s="65" t="n"/>
+      <c r="G24" s="65" t="n"/>
+      <c r="H24" s="65" t="n"/>
+      <c r="I24" s="65" t="n"/>
+      <c r="J24" s="65" t="n"/>
+      <c r="K24" s="65" t="n"/>
+      <c r="L24" s="65" t="n"/>
+      <c r="M24" s="65" t="n"/>
+      <c r="N24" s="65" t="n"/>
+      <c r="O24" s="65" t="n"/>
+      <c r="P24" s="65" t="n"/>
+      <c r="Q24" s="65" t="n"/>
+      <c r="R24" s="65" t="n"/>
+      <c r="S24" s="65" t="n"/>
+      <c r="T24" s="65" t="n"/>
+      <c r="U24" s="67">
         <f>COUNTIF(U6:U22,"Tercapai")&amp;" dari "&amp;(ROWS(U6:U22)-COUNTIF(U6:U22,"Belum diukur"))</f>
         <v/>
       </c>
@@ -2153,7 +2363,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="8" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -2161,7 +2371,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -2292,6 +2502,6 @@
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>